--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/124.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/124.xlsx
@@ -426,13 +426,13 @@
         <v>-13.22242363705205</v>
       </c>
       <c r="E2">
-        <v>-19.17331195911347</v>
+        <v>-17.20325368376458</v>
       </c>
       <c r="F2">
-        <v>-5.330281791795639</v>
+        <v>-6.025767466042464</v>
       </c>
       <c r="G2">
-        <v>-14.03166896577632</v>
+        <v>-13.3710032557772</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.75191589496462</v>
       </c>
       <c r="E3">
-        <v>-18.47197360412354</v>
+        <v>-17.60465309133047</v>
       </c>
       <c r="F3">
-        <v>-5.927272096747395</v>
+        <v>-6.34799575879225</v>
       </c>
       <c r="G3">
-        <v>-13.87098170639117</v>
+        <v>-13.30944366147446</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.26361898303692</v>
       </c>
       <c r="E4">
-        <v>-19.40572230213513</v>
+        <v>-19.0612141135276</v>
       </c>
       <c r="F4">
-        <v>-5.650556794209623</v>
+        <v>-6.188852298468618</v>
       </c>
       <c r="G4">
-        <v>-14.20114572356823</v>
+        <v>-12.85200572104012</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.82368541334999</v>
       </c>
       <c r="E5">
-        <v>-19.64460836298776</v>
+        <v>-19.43193763816554</v>
       </c>
       <c r="F5">
-        <v>-5.555493351064352</v>
+        <v>-6.151840014544133</v>
       </c>
       <c r="G5">
-        <v>-12.83176835615856</v>
+        <v>-12.57058617638329</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.42786546205236</v>
       </c>
       <c r="E6">
-        <v>-19.38668459740688</v>
+        <v>-19.99159815535149</v>
       </c>
       <c r="F6">
-        <v>-5.595361017426287</v>
+        <v>-5.942185195099994</v>
       </c>
       <c r="G6">
-        <v>-12.08747495529191</v>
+        <v>-12.88414118658982</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.09224096940591</v>
       </c>
       <c r="E7">
-        <v>-21.49691725718921</v>
+        <v>-20.60716268416214</v>
       </c>
       <c r="F7">
-        <v>-5.666842497348661</v>
+        <v>-5.962461972385721</v>
       </c>
       <c r="G7">
-        <v>-12.78785396958012</v>
+        <v>-12.64042213453422</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.79306849335179</v>
       </c>
       <c r="E8">
-        <v>-21.48688668726222</v>
+        <v>-21.07511254574476</v>
       </c>
       <c r="F8">
-        <v>-5.692814300528634</v>
+        <v>-5.884827379395351</v>
       </c>
       <c r="G8">
-        <v>-11.77248316832133</v>
+        <v>-11.87323631126351</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.5249035094964</v>
       </c>
       <c r="E9">
-        <v>-21.49634666946424</v>
+        <v>-20.86970549323084</v>
       </c>
       <c r="F9">
-        <v>-5.976723145592318</v>
+        <v>-6.230831473340288</v>
       </c>
       <c r="G9">
-        <v>-12.88185691016773</v>
+        <v>-12.23927008935857</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.267377445577</v>
       </c>
       <c r="E10">
-        <v>-22.28483097825778</v>
+        <v>-22.38073500079223</v>
       </c>
       <c r="F10">
-        <v>-6.141427436290943</v>
+        <v>-5.970912148261679</v>
       </c>
       <c r="G10">
-        <v>-12.72815159132491</v>
+        <v>-11.55455326601665</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.00490388254066</v>
       </c>
       <c r="E11">
-        <v>-22.87490472687925</v>
+        <v>-21.87046202113392</v>
       </c>
       <c r="F11">
-        <v>-5.645941131041224</v>
+        <v>-6.008644283459196</v>
       </c>
       <c r="G11">
-        <v>-12.13389211429803</v>
+        <v>-11.73351142623303</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.742969100312951</v>
       </c>
       <c r="E12">
-        <v>-24.32873507924976</v>
+        <v>-22.9571146440145</v>
       </c>
       <c r="F12">
-        <v>-5.518402372236601</v>
+        <v>-5.82747619062993</v>
       </c>
       <c r="G12">
-        <v>-11.20205961917721</v>
+        <v>-11.75504983551153</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.477584009629798</v>
       </c>
       <c r="E13">
-        <v>-24.85483507556487</v>
+        <v>-23.35931106300574</v>
       </c>
       <c r="F13">
-        <v>-5.220959660545979</v>
+        <v>-5.914212884642261</v>
       </c>
       <c r="G13">
-        <v>-10.36257479187437</v>
+        <v>-11.55820479774647</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.227188702788627</v>
       </c>
       <c r="E14">
-        <v>-24.62311306059238</v>
+        <v>-24.72731324750887</v>
       </c>
       <c r="F14">
-        <v>-5.477779234803314</v>
+        <v>-5.31652592270475</v>
       </c>
       <c r="G14">
-        <v>-11.15294105501105</v>
+        <v>-10.95910861368672</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.011077476714032</v>
       </c>
       <c r="E15">
-        <v>-26.31097494967929</v>
+        <v>-24.74319460585378</v>
       </c>
       <c r="F15">
-        <v>-5.2705581587886</v>
+        <v>-5.440906944969901</v>
       </c>
       <c r="G15">
-        <v>-10.38172298727351</v>
+        <v>-10.79286956943222</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.840349254002993</v>
       </c>
       <c r="E16">
-        <v>-27.01343636622313</v>
+        <v>-26.22393315077786</v>
       </c>
       <c r="F16">
-        <v>-4.974700113939535</v>
+        <v>-5.235155392727755</v>
       </c>
       <c r="G16">
-        <v>-9.999209313483959</v>
+        <v>-10.41166356113068</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.740133218536371</v>
       </c>
       <c r="E17">
-        <v>-27.17160690636303</v>
+        <v>-26.27670798686325</v>
       </c>
       <c r="F17">
-        <v>-5.320584922978468</v>
+        <v>-5.127061730336448</v>
       </c>
       <c r="G17">
-        <v>-9.760353452825543</v>
+        <v>-10.22270424284016</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.715051119230608</v>
       </c>
       <c r="E18">
-        <v>-28.18860707053163</v>
+        <v>-26.71957463091738</v>
       </c>
       <c r="F18">
-        <v>-5.199743514625479</v>
+        <v>-4.708335262099742</v>
       </c>
       <c r="G18">
-        <v>-10.20388048090386</v>
+        <v>-10.53991740586758</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.765958075680448</v>
       </c>
       <c r="E19">
-        <v>-28.47009248637442</v>
+        <v>-27.86047384393584</v>
       </c>
       <c r="F19">
-        <v>-4.368555520819441</v>
+        <v>-4.689880893100175</v>
       </c>
       <c r="G19">
-        <v>-9.437456083107188</v>
+        <v>-10.40358583001486</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.89313447669196</v>
       </c>
       <c r="E20">
-        <v>-28.20858669785348</v>
+        <v>-27.7638045092941</v>
       </c>
       <c r="F20">
-        <v>-3.998900709157176</v>
+        <v>-4.460456257220824</v>
       </c>
       <c r="G20">
-        <v>-9.814566946576647</v>
+        <v>-10.49841971753282</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.074952928587113</v>
       </c>
       <c r="E21">
-        <v>-29.58847839086375</v>
+        <v>-28.4291686667671</v>
       </c>
       <c r="F21">
-        <v>-4.05602823872384</v>
+        <v>-3.923215264665593</v>
       </c>
       <c r="G21">
-        <v>-10.16441546753021</v>
+        <v>-10.31160232220621</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.298594132430239</v>
       </c>
       <c r="E22">
-        <v>-29.76923695935392</v>
+        <v>-28.74407422078649</v>
       </c>
       <c r="F22">
-        <v>-3.867601162343843</v>
+        <v>-3.943788597481522</v>
       </c>
       <c r="G22">
-        <v>-8.666390300464458</v>
+        <v>-10.84705988936455</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.538188316441881</v>
       </c>
       <c r="E23">
-        <v>-29.65533451687599</v>
+        <v>-28.53224126365568</v>
       </c>
       <c r="F23">
-        <v>-4.330684219898253</v>
+        <v>-3.796840362061903</v>
       </c>
       <c r="G23">
-        <v>-8.722444457535397</v>
+        <v>-10.65253885456805</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.762865751265212</v>
       </c>
       <c r="E24">
-        <v>-30.2358690350003</v>
+        <v>-29.40287209094837</v>
       </c>
       <c r="F24">
-        <v>-4.121381456600305</v>
+        <v>-3.608236015057706</v>
       </c>
       <c r="G24">
-        <v>-9.20551595208031</v>
+        <v>-10.15718854661798</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.955249324636677</v>
       </c>
       <c r="E25">
-        <v>-30.04401796942834</v>
+        <v>-28.92538073463159</v>
       </c>
       <c r="F25">
-        <v>-3.376328762072165</v>
+        <v>-3.486074189064655</v>
       </c>
       <c r="G25">
-        <v>-10.87491813007751</v>
+        <v>-10.75647012122793</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.08545884192247</v>
       </c>
       <c r="E26">
-        <v>-30.46214782421557</v>
+        <v>-29.7352801970074</v>
       </c>
       <c r="F26">
-        <v>-3.194303308981002</v>
+        <v>-3.262274167850312</v>
       </c>
       <c r="G26">
-        <v>-9.579975068572812</v>
+        <v>-10.92822122380532</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.14326710541623</v>
       </c>
       <c r="E27">
-        <v>-30.72532914811935</v>
+        <v>-29.48995011764186</v>
       </c>
       <c r="F27">
-        <v>-3.417432352599076</v>
+        <v>-2.950377273348242</v>
       </c>
       <c r="G27">
-        <v>-10.81825814317289</v>
+        <v>-11.58282201437649</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.12585565926312</v>
       </c>
       <c r="E28">
-        <v>-30.19332402169824</v>
+        <v>-29.0746347094504</v>
       </c>
       <c r="F28">
-        <v>-3.666883598808508</v>
+        <v>-3.28984223501548</v>
       </c>
       <c r="G28">
-        <v>-10.42525004002385</v>
+        <v>-10.97393985770265</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.03378299933585</v>
       </c>
       <c r="E29">
-        <v>-29.44707905421124</v>
+        <v>-29.30113539389204</v>
       </c>
       <c r="F29">
-        <v>-3.533409587562827</v>
+        <v>-3.243634244552518</v>
       </c>
       <c r="G29">
-        <v>-9.791810256539698</v>
+        <v>-11.29166946583421</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.890726803605782</v>
       </c>
       <c r="E30">
-        <v>-30.48904243134713</v>
+        <v>-28.98831293791618</v>
       </c>
       <c r="F30">
-        <v>-2.993223748890644</v>
+        <v>-3.084037667259554</v>
       </c>
       <c r="G30">
-        <v>-11.54946164697725</v>
+        <v>-11.17537331158515</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.713384460977329</v>
       </c>
       <c r="E31">
-        <v>-29.70538774008277</v>
+        <v>-28.89413426397866</v>
       </c>
       <c r="F31">
-        <v>-3.175596287923581</v>
+        <v>-2.874608163748977</v>
       </c>
       <c r="G31">
-        <v>-10.7481639624699</v>
+        <v>-11.59452810340335</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.525415402286134</v>
       </c>
       <c r="E32">
-        <v>-29.17597742926805</v>
+        <v>-29.04429846207301</v>
       </c>
       <c r="F32">
-        <v>-3.26535072438431</v>
+        <v>-3.314573972193462</v>
       </c>
       <c r="G32">
-        <v>-10.31340325897957</v>
+        <v>-11.90249491273959</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.353276675873802</v>
       </c>
       <c r="E33">
-        <v>-28.67899099234825</v>
+        <v>-29.03600682616497</v>
       </c>
       <c r="F33">
-        <v>-3.321128843451814</v>
+        <v>-3.329957583230851</v>
       </c>
       <c r="G33">
-        <v>-10.20084802118989</v>
+        <v>-11.38088535757202</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.205910114377421</v>
       </c>
       <c r="E34">
-        <v>-29.42853042467583</v>
+        <v>-27.5213907671895</v>
       </c>
       <c r="F34">
-        <v>-3.232008108054227</v>
+        <v>-3.152718436993064</v>
       </c>
       <c r="G34">
-        <v>-9.546869613180101</v>
+        <v>-11.18827119700615</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.100051386114368</v>
       </c>
       <c r="E35">
-        <v>-27.70976170048657</v>
+        <v>-28.63479308603339</v>
       </c>
       <c r="F35">
-        <v>-2.849455615930373</v>
+        <v>-3.458779483142411</v>
       </c>
       <c r="G35">
-        <v>-10.80840595964801</v>
+        <v>-10.88611108454579</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.036845333097624</v>
       </c>
       <c r="E36">
-        <v>-29.54923010663927</v>
+        <v>-28.00720998720638</v>
       </c>
       <c r="F36">
-        <v>-3.499508651603257</v>
+        <v>-3.029818535644118</v>
       </c>
       <c r="G36">
-        <v>-9.733293053587541</v>
+        <v>-11.30864925390513</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.00936012513881</v>
       </c>
       <c r="E37">
-        <v>-27.13500325095903</v>
+        <v>-27.08903923978118</v>
       </c>
       <c r="F37">
-        <v>-3.815481113727101</v>
+        <v>-3.275771586311528</v>
       </c>
       <c r="G37">
-        <v>-10.83820086950146</v>
+        <v>-10.75934036421048</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.019202535361554</v>
       </c>
       <c r="E38">
-        <v>-28.28471940287043</v>
+        <v>-27.53976731471263</v>
       </c>
       <c r="F38">
-        <v>-2.823245242938394</v>
+        <v>-3.023381292556963</v>
       </c>
       <c r="G38">
-        <v>-10.1911712965786</v>
+        <v>-10.84836424430702</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.049164989971723</v>
       </c>
       <c r="E39">
-        <v>-27.49168850617319</v>
+        <v>-26.76788892010521</v>
       </c>
       <c r="F39">
-        <v>-3.481743484282819</v>
+        <v>-3.339500375711102</v>
       </c>
       <c r="G39">
-        <v>-10.51759439729628</v>
+        <v>-10.1927305635276</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.09628132900899</v>
       </c>
       <c r="E40">
-        <v>-26.15396369888535</v>
+        <v>-25.97195074309505</v>
       </c>
       <c r="F40">
-        <v>-3.450933187103094</v>
+        <v>-3.212563840008314</v>
       </c>
       <c r="G40">
-        <v>-10.75137188109745</v>
+        <v>-11.20843572988585</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.15406178024131</v>
       </c>
       <c r="E41">
-        <v>-26.14765100611865</v>
+        <v>-25.85948156264055</v>
       </c>
       <c r="F41">
-        <v>-3.126888284638969</v>
+        <v>-3.355213676974806</v>
       </c>
       <c r="G41">
-        <v>-10.58134557274602</v>
+        <v>-10.13314074382071</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.210870580090747</v>
       </c>
       <c r="E42">
-        <v>-27.41431952775214</v>
+        <v>-25.60161666722178</v>
       </c>
       <c r="F42">
-        <v>-3.36653000406445</v>
+        <v>-3.303218711835886</v>
       </c>
       <c r="G42">
-        <v>-9.526046281738086</v>
+        <v>-9.710920386833147</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.271074306939619</v>
       </c>
       <c r="E43">
-        <v>-25.8040122845206</v>
+        <v>-24.94463924361098</v>
       </c>
       <c r="F43">
-        <v>-3.576338899845509</v>
+        <v>-3.398729473378669</v>
       </c>
       <c r="G43">
-        <v>-10.43996541494591</v>
+        <v>-10.39764009022633</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.326098051187218</v>
       </c>
       <c r="E44">
-        <v>-25.7949236371872</v>
+        <v>-24.53268396313321</v>
       </c>
       <c r="F44">
-        <v>-3.72514930518662</v>
+        <v>-3.395959412783708</v>
       </c>
       <c r="G44">
-        <v>-9.406105216850291</v>
+        <v>-10.37289045177473</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.376699739923382</v>
       </c>
       <c r="E45">
-        <v>-23.06880492693968</v>
+        <v>-23.83673449221241</v>
       </c>
       <c r="F45">
-        <v>-3.448515182654322</v>
+        <v>-3.44500207649905</v>
       </c>
       <c r="G45">
-        <v>-8.573969800644624</v>
+        <v>-10.15061380317699</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.426365313655062</v>
       </c>
       <c r="E46">
-        <v>-23.84085087508538</v>
+        <v>-23.0162112298146</v>
       </c>
       <c r="F46">
-        <v>-3.377810711355774</v>
+        <v>-3.319139933317693</v>
       </c>
       <c r="G46">
-        <v>-9.355387659188656</v>
+        <v>-10.41993330388778</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.467398009760876</v>
       </c>
       <c r="E47">
-        <v>-22.17368864068753</v>
+        <v>-22.55291211103786</v>
       </c>
       <c r="F47">
-        <v>-3.543096515971164</v>
+        <v>-3.45473705021675</v>
       </c>
       <c r="G47">
-        <v>-9.374684829137067</v>
+        <v>-10.20113272810627</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.505827800859581</v>
       </c>
       <c r="E48">
-        <v>-22.14927110883817</v>
+        <v>-22.77405561072844</v>
       </c>
       <c r="F48">
-        <v>-3.542573816139998</v>
+        <v>-3.428786784589249</v>
       </c>
       <c r="G48">
-        <v>-9.63449975360461</v>
+        <v>-10.04455054518982</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.537517874538048</v>
       </c>
       <c r="E49">
-        <v>-22.46458875399226</v>
+        <v>-21.8230987114877</v>
       </c>
       <c r="F49">
-        <v>-3.773147397607032</v>
+        <v>-3.427618786551302</v>
       </c>
       <c r="G49">
-        <v>-8.778048380412997</v>
+        <v>-10.71927283154868</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.557574200003479</v>
       </c>
       <c r="E50">
-        <v>-20.93620613403348</v>
+        <v>-21.44697724583262</v>
       </c>
       <c r="F50">
-        <v>-3.452618914767791</v>
+        <v>-3.878766726566177</v>
       </c>
       <c r="G50">
-        <v>-9.395779625313304</v>
+        <v>-10.62136013667919</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.569967037720529</v>
       </c>
       <c r="E51">
-        <v>-21.26812969337369</v>
+        <v>-20.14389526470345</v>
       </c>
       <c r="F51">
-        <v>-3.959998919186905</v>
+        <v>-3.801707848920753</v>
       </c>
       <c r="G51">
-        <v>-9.375270795697519</v>
+        <v>-10.54782298861536</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.562595871470075</v>
       </c>
       <c r="E52">
-        <v>-20.85583477734534</v>
+        <v>-20.69834803678059</v>
       </c>
       <c r="F52">
-        <v>-3.468039802338307</v>
+        <v>-3.524708416363821</v>
       </c>
       <c r="G52">
-        <v>-9.003920281466391</v>
+        <v>-9.965577481350504</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.536193695307301</v>
       </c>
       <c r="E53">
-        <v>-20.08560927575073</v>
+        <v>-19.67454157617846</v>
       </c>
       <c r="F53">
-        <v>-3.564356565364013</v>
+        <v>-3.873924919096814</v>
       </c>
       <c r="G53">
-        <v>-9.868204405403921</v>
+        <v>-9.994190526446424</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.485788507356627</v>
       </c>
       <c r="E54">
-        <v>-20.71309274814956</v>
+        <v>-19.86414878287962</v>
       </c>
       <c r="F54">
-        <v>-3.751384529200683</v>
+        <v>-3.89681436717097</v>
       </c>
       <c r="G54">
-        <v>-9.888110715731557</v>
+        <v>-10.2947417137747</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.402845410231516</v>
       </c>
       <c r="E55">
-        <v>-19.35699139333859</v>
+        <v>-19.87403897011237</v>
       </c>
       <c r="F55">
-        <v>-3.906512064355544</v>
+        <v>-4.02152922149945</v>
       </c>
       <c r="G55">
-        <v>-10.28428701096168</v>
+        <v>-10.76853374917303</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.29116089327956</v>
       </c>
       <c r="E56">
-        <v>-17.69115147335098</v>
+        <v>-19.4346320802001</v>
       </c>
       <c r="F56">
-        <v>-3.346005544925287</v>
+        <v>-3.999257735507782</v>
       </c>
       <c r="G56">
-        <v>-10.24355074810095</v>
+        <v>-10.68225431132855</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.141039273094355</v>
       </c>
       <c r="E57">
-        <v>-20.07340050982605</v>
+        <v>-18.75405225006133</v>
       </c>
       <c r="F57">
-        <v>-4.247091180179547</v>
+        <v>-3.751165840206344</v>
       </c>
       <c r="G57">
-        <v>-10.92907534455445</v>
+        <v>-10.56498485669094</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.955263142208324</v>
       </c>
       <c r="E58">
-        <v>-17.66299795044529</v>
+        <v>-19.04905968929101</v>
       </c>
       <c r="F58">
-        <v>-3.872326998376814</v>
+        <v>-3.430170986519328</v>
       </c>
       <c r="G58">
-        <v>-11.01705640280612</v>
+        <v>-10.60165576962945</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.736326552389444</v>
       </c>
       <c r="E59">
-        <v>-18.15877075633104</v>
+        <v>-17.66421158147935</v>
       </c>
       <c r="F59">
-        <v>-3.9010249586794</v>
+        <v>-3.950464410380683</v>
       </c>
       <c r="G59">
-        <v>-11.26331133274481</v>
+        <v>-10.99261133454414</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.481463213475665</v>
       </c>
       <c r="E60">
-        <v>-19.31556944159043</v>
+        <v>-17.45431681122383</v>
       </c>
       <c r="F60">
-        <v>-3.700466441685403</v>
+        <v>-3.613034747422124</v>
       </c>
       <c r="G60">
-        <v>-10.02395233084447</v>
+        <v>-11.08938520174812</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.201917430048857</v>
       </c>
       <c r="E61">
-        <v>-17.37271823807962</v>
+        <v>-17.67882043862809</v>
       </c>
       <c r="F61">
-        <v>-4.051146669619143</v>
+        <v>-3.825700682375438</v>
       </c>
       <c r="G61">
-        <v>-11.08931568029179</v>
+        <v>-10.99185653016119</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.90040721029054</v>
       </c>
       <c r="E62">
-        <v>-17.02760323395506</v>
+        <v>-17.34456924364794</v>
       </c>
       <c r="F62">
-        <v>-3.777646260971636</v>
+        <v>-3.808063912002434</v>
       </c>
       <c r="G62">
-        <v>-11.07729839998424</v>
+        <v>-11.41817534252638</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.584973737513882</v>
       </c>
       <c r="E63">
-        <v>-17.82802460023282</v>
+        <v>-17.58178882606574</v>
       </c>
       <c r="F63">
-        <v>-3.756798738545381</v>
+        <v>-4.042334497188162</v>
       </c>
       <c r="G63">
-        <v>-10.48633291576894</v>
+        <v>-11.57165554427253</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.267682640318194</v>
       </c>
       <c r="E64">
-        <v>-17.84379274672753</v>
+        <v>-16.92113881003473</v>
       </c>
       <c r="F64">
-        <v>-4.041343769774413</v>
+        <v>-3.661109878010996</v>
       </c>
       <c r="G64">
-        <v>-10.74698871880346</v>
+        <v>-11.29076899744752</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.949495944701647</v>
       </c>
       <c r="E65">
-        <v>-16.34307910295561</v>
+        <v>-15.94403903034771</v>
       </c>
       <c r="F65">
-        <v>-4.02239320870057</v>
+        <v>-4.065629845289689</v>
       </c>
       <c r="G65">
-        <v>-11.73106493307951</v>
+        <v>-11.92751932647094</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.641928441150326</v>
       </c>
       <c r="E66">
-        <v>-16.79831753799869</v>
+        <v>-16.87358983295419</v>
       </c>
       <c r="F66">
-        <v>-3.930387269639031</v>
+        <v>-3.894668067230317</v>
       </c>
       <c r="G66">
-        <v>-10.04786109072909</v>
+        <v>-11.67676536514439</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.348101832532354</v>
       </c>
       <c r="E67">
-        <v>-18.15062856006525</v>
+        <v>-16.0263304600151</v>
       </c>
       <c r="F67">
-        <v>-3.908908531251843</v>
+        <v>-3.993343192251793</v>
       </c>
       <c r="G67">
-        <v>-11.80419488404201</v>
+        <v>-11.85027436740313</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.070343534484516</v>
       </c>
       <c r="E68">
-        <v>-16.90521669542376</v>
+        <v>-15.61655337553501</v>
       </c>
       <c r="F68">
-        <v>-3.632809534061753</v>
+        <v>-4.007683888729058</v>
       </c>
       <c r="G68">
-        <v>-11.5210141291583</v>
+        <v>-11.62454150926238</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.817307047190222</v>
       </c>
       <c r="E69">
-        <v>-15.83822670668449</v>
+        <v>-17.05676660656446</v>
       </c>
       <c r="F69">
-        <v>-3.579352500456893</v>
+        <v>-4.08631914954201</v>
       </c>
       <c r="G69">
-        <v>-11.15641712782728</v>
+        <v>-12.03369183246091</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.582786418027232</v>
       </c>
       <c r="E70">
-        <v>-17.74684264669731</v>
+        <v>-15.85420316298355</v>
       </c>
       <c r="F70">
-        <v>-3.569845327774963</v>
+        <v>-4.137857684241987</v>
       </c>
       <c r="G70">
-        <v>-11.13445165817422</v>
+        <v>-11.87915225614219</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.367452004467526</v>
       </c>
       <c r="E71">
-        <v>-16.74801524872149</v>
+        <v>-16.99284266747218</v>
       </c>
       <c r="F71">
-        <v>-4.137330014206404</v>
+        <v>-4.324012548836106</v>
       </c>
       <c r="G71">
-        <v>-11.13647440149871</v>
+        <v>-11.51985212767401</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.164340469443402</v>
       </c>
       <c r="E72">
-        <v>-17.79538788805954</v>
+        <v>-16.46376293526002</v>
       </c>
       <c r="F72">
-        <v>-3.945572900867152</v>
+        <v>-4.350059733449734</v>
       </c>
       <c r="G72">
-        <v>-11.6818669158204</v>
+        <v>-10.99604768081391</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.962465197956061</v>
       </c>
       <c r="E73">
-        <v>-17.50601387049539</v>
+        <v>-16.85029536265873</v>
       </c>
       <c r="F73">
-        <v>-4.488198281540579</v>
+        <v>-4.417407660032139</v>
       </c>
       <c r="G73">
-        <v>-10.02536593378974</v>
+        <v>-11.5526861183325</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.757901289795315</v>
       </c>
       <c r="E74">
-        <v>-16.89755451740278</v>
+        <v>-16.0804683667768</v>
       </c>
       <c r="F74">
-        <v>-4.178634898012196</v>
+        <v>-4.434591313435812</v>
       </c>
       <c r="G74">
-        <v>-10.42734892589574</v>
+        <v>-11.45712722134144</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.538999866529698</v>
       </c>
       <c r="E75">
-        <v>-17.3289595937435</v>
+        <v>-16.91189619458507</v>
       </c>
       <c r="F75">
-        <v>-4.389344229160097</v>
+        <v>-4.595984619625448</v>
       </c>
       <c r="G75">
-        <v>-10.32993612340269</v>
+        <v>-11.3237784470196</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.301497762109725</v>
       </c>
       <c r="E76">
-        <v>-18.98712375028811</v>
+        <v>-16.87063726790119</v>
       </c>
       <c r="F76">
-        <v>-4.57427228163067</v>
+        <v>-4.388206880716053</v>
       </c>
       <c r="G76">
-        <v>-10.08803787139368</v>
+        <v>-11.50412041527139</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.043982628117197</v>
       </c>
       <c r="E77">
-        <v>-17.8664487021879</v>
+        <v>-17.27224045679743</v>
       </c>
       <c r="F77">
-        <v>-4.336605390093464</v>
+        <v>-4.754216875806001</v>
       </c>
       <c r="G77">
-        <v>-11.0355921472805</v>
+        <v>-10.79322379780492</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.763726653039274</v>
       </c>
       <c r="E78">
-        <v>-17.90439278589817</v>
+        <v>-18.59806443439312</v>
       </c>
       <c r="F78">
-        <v>-4.488025152753394</v>
+        <v>-4.733033864581612</v>
       </c>
       <c r="G78">
-        <v>-10.66798586005429</v>
+        <v>-10.53876533601992</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.468320775840009</v>
       </c>
       <c r="E79">
-        <v>-19.75982632716492</v>
+        <v>-18.13179010819334</v>
       </c>
       <c r="F79">
-        <v>-4.843108981800416</v>
+        <v>-4.807991174126133</v>
       </c>
       <c r="G79">
-        <v>-10.88465113396297</v>
+        <v>-11.40348976251417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.164260092389291</v>
       </c>
       <c r="E80">
-        <v>-19.82181660785592</v>
+        <v>-19.3976163336614</v>
       </c>
       <c r="F80">
-        <v>-4.82488572730623</v>
+        <v>-4.787840308685633</v>
       </c>
       <c r="G80">
-        <v>-9.62259834239093</v>
+        <v>-11.33019759482024</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.861370345878798</v>
       </c>
       <c r="E81">
-        <v>-19.18809289827451</v>
+        <v>-19.42714198419141</v>
       </c>
       <c r="F81">
-        <v>-4.906565238324469</v>
+        <v>-4.862912761299144</v>
       </c>
       <c r="G81">
-        <v>-11.04488815915477</v>
+        <v>-11.36372348949644</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.573316531551918</v>
       </c>
       <c r="E82">
-        <v>-21.21416386862428</v>
+        <v>-19.17617848316033</v>
       </c>
       <c r="F82">
-        <v>-4.931195086311907</v>
+        <v>-4.78257851894305</v>
       </c>
       <c r="G82">
-        <v>-10.3235467705119</v>
+        <v>-9.768560295217396</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.307542489514665</v>
       </c>
       <c r="E83">
-        <v>-21.19091015459489</v>
+        <v>-21.31055243787754</v>
       </c>
       <c r="F83">
-        <v>-4.835250260250057</v>
+        <v>-5.433184075673602</v>
       </c>
       <c r="G83">
-        <v>-9.579243438008634</v>
+        <v>-10.64602039040122</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.077195399190714</v>
       </c>
       <c r="E84">
-        <v>-23.02838829642123</v>
+        <v>-21.72266168647158</v>
       </c>
       <c r="F84">
-        <v>-5.486947605217498</v>
+        <v>-5.43771358863211</v>
       </c>
       <c r="G84">
-        <v>-9.967649882858087</v>
+        <v>-10.00097714480193</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.892534687487687</v>
       </c>
       <c r="E85">
-        <v>-21.57146499630348</v>
+        <v>-21.90077562614127</v>
       </c>
       <c r="F85">
-        <v>-5.143222349997663</v>
+        <v>-5.269461400347294</v>
       </c>
       <c r="G85">
-        <v>-9.326648813362242</v>
+        <v>-9.812792494167599</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.760202176582247</v>
       </c>
       <c r="E86">
-        <v>-23.56466830230558</v>
+        <v>-23.22037748045042</v>
       </c>
       <c r="F86">
-        <v>-5.312411421815045</v>
+        <v>-5.127637445681393</v>
       </c>
       <c r="G86">
-        <v>-9.255836244277232</v>
+        <v>-9.392296931405991</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.692346549347413</v>
       </c>
       <c r="E87">
-        <v>-25.37392952259012</v>
+        <v>-23.69428228535312</v>
       </c>
       <c r="F87">
-        <v>-5.793008651366845</v>
+        <v>-5.432419492560818</v>
       </c>
       <c r="G87">
-        <v>-9.357721593793842</v>
+        <v>-9.507209277619632</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.6947228465087</v>
       </c>
       <c r="E88">
-        <v>-24.39555724170695</v>
+        <v>-25.27750019707079</v>
       </c>
       <c r="F88">
-        <v>-5.651187181803153</v>
+        <v>-5.831331412522559</v>
       </c>
       <c r="G88">
-        <v>-10.45393260657609</v>
+        <v>-9.986629240434729</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.774638214214665</v>
       </c>
       <c r="E89">
-        <v>-26.61636617980857</v>
+        <v>-25.83428060478786</v>
       </c>
       <c r="F89">
-        <v>-5.560422965478412</v>
+        <v>-5.918400281863413</v>
       </c>
       <c r="G89">
-        <v>-9.47924178890387</v>
+        <v>-9.751987704247805</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.940593384854141</v>
       </c>
       <c r="E90">
-        <v>-27.83880962428315</v>
+        <v>-28.364760180956</v>
       </c>
       <c r="F90">
-        <v>-5.646060415947227</v>
+        <v>-5.810073019864515</v>
       </c>
       <c r="G90">
-        <v>-9.52870796035166</v>
+        <v>-9.622681106029411</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.191617421146487</v>
       </c>
       <c r="E91">
-        <v>-29.50386158979342</v>
+        <v>-29.43535483500538</v>
       </c>
       <c r="F91">
-        <v>-5.648456882843527</v>
+        <v>-6.12250089787178</v>
       </c>
       <c r="G91">
-        <v>-10.04042891599343</v>
+        <v>-9.815109876045089</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.531023929887131</v>
       </c>
       <c r="E92">
-        <v>-30.75871079426689</v>
+        <v>-31.11977961232047</v>
       </c>
       <c r="F92">
-        <v>-5.859292125836654</v>
+        <v>-5.956690736690416</v>
       </c>
       <c r="G92">
-        <v>-9.794558009337292</v>
+        <v>-9.579561250380404</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.956041384592731</v>
       </c>
       <c r="E93">
-        <v>-32.42550169379611</v>
+        <v>-32.37520619722992</v>
       </c>
       <c r="F93">
-        <v>-6.339003002267458</v>
+        <v>-6.360610551785782</v>
       </c>
       <c r="G93">
-        <v>-9.959171575732013</v>
+        <v>-9.71176457594566</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.456589836902722</v>
       </c>
       <c r="E94">
-        <v>-34.66383809054442</v>
+        <v>-34.42713022568949</v>
       </c>
       <c r="F94">
-        <v>-6.525041067057782</v>
+        <v>-6.306970863168605</v>
       </c>
       <c r="G94">
-        <v>-10.97737289342688</v>
+        <v>-10.20311905542983</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.025011650031172</v>
       </c>
       <c r="E95">
-        <v>-35.09933464315107</v>
+        <v>-36.62816105356261</v>
       </c>
       <c r="F95">
-        <v>-6.426243757844393</v>
+        <v>-6.698185593223532</v>
       </c>
       <c r="G95">
-        <v>-10.20182132157843</v>
+        <v>-9.777124676527491</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.643311681835888</v>
       </c>
       <c r="E96">
-        <v>-36.86008911410244</v>
+        <v>-37.85175925890914</v>
       </c>
       <c r="F96">
-        <v>-6.732311845116664</v>
+        <v>-6.80818491482498</v>
       </c>
       <c r="G96">
-        <v>-9.90376959613231</v>
+        <v>-10.96231322176873</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.285754981698034</v>
       </c>
       <c r="E97">
-        <v>-39.01297320632602</v>
+        <v>-40.36437853359104</v>
       </c>
       <c r="F97">
-        <v>-6.912845408515385</v>
+        <v>-6.911645104148729</v>
       </c>
       <c r="G97">
-        <v>-10.42441909309349</v>
+        <v>-11.66680724416226</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.94276350044073</v>
       </c>
       <c r="E98">
-        <v>-42.69400670209697</v>
+        <v>-42.19771312170035</v>
       </c>
       <c r="F98">
-        <v>-7.038770093435653</v>
+        <v>-7.092497588997528</v>
       </c>
       <c r="G98">
-        <v>-11.38101446884806</v>
+        <v>-11.68066187724411</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.572495698293205</v>
       </c>
       <c r="E99">
-        <v>-44.9000618718816</v>
+        <v>-43.64825806617829</v>
       </c>
       <c r="F99">
-        <v>-7.02816988996573</v>
+        <v>-7.372875103823077</v>
       </c>
       <c r="G99">
-        <v>-11.71578676541578</v>
+        <v>-11.76302825026118</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.186494427900239</v>
       </c>
       <c r="E100">
-        <v>-45.05401413848337</v>
+        <v>-46.29125663601501</v>
       </c>
       <c r="F100">
-        <v>-7.678784972921413</v>
+        <v>-7.759240156918315</v>
       </c>
       <c r="G100">
-        <v>-12.3440654084042</v>
+        <v>-12.2958539337158</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.723311793441371</v>
       </c>
       <c r="E101">
-        <v>-47.01886919719745</v>
+        <v>-48.44723933657833</v>
       </c>
       <c r="F101">
-        <v>-7.546923793008983</v>
+        <v>-7.405047237013004</v>
       </c>
       <c r="G101">
-        <v>-12.38452689598518</v>
+        <v>-12.454270158861</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.238904898291933</v>
       </c>
       <c r="E102">
-        <v>-49.83827107564747</v>
+        <v>-50.2567507550518</v>
       </c>
       <c r="F102">
-        <v>-7.612997690525882</v>
+        <v>-7.542747578747768</v>
       </c>
       <c r="G102">
-        <v>-11.89078220262165</v>
+        <v>-12.97569432347837</v>
       </c>
     </row>
   </sheetData>
